--- a/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
+++ b/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-30T22:57:21+01:00</t>
+    <t>2025-12-18T07:21:20+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
@@ -344,7 +344,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/RetinaIntegration/ValueSet/retina-conclusioncode-vs</t>
+    <t>http://dips.no/fhir/RetinaIntegration/ValueSet/retina-conclusion-code-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -673,7 +673,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.1015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.73046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -688,7 +688,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.91015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
+++ b/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T09:57:13+01:00</t>
+    <t>2026-03-31T17:09:32+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
+++ b/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.8.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T17:09:32+02:00</t>
+    <t>2026-04-17T16:52:07+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
+++ b/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T16:52:07+02:00</t>
+    <t>2026-05-08T13:22:39+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
+++ b/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:22:39+02:00</t>
+    <t>2026-06-05T15:47:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
+++ b/docs/StructureDefinition-previous-examination-conclusion-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T15:47:27+02:00</t>
+    <t>2026-06-08T15:50:57+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
